--- a/docs/요구사항_정의서_v1.0_CKD.xlsx
+++ b/docs/요구사항_정의서_v1.0_CKD.xlsx
@@ -2083,8 +2083,8 @@
   <mergeCells count="4">
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A1:B1"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -2527,7 +2527,7 @@
       <c r="I8" s="19" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="K8" s="11" t="n"/>

--- a/docs/요구사항_정의서_v1.0_CKD.xlsx
+++ b/docs/요구사항_정의서_v1.0_CKD.xlsx
@@ -2083,8 +2083,8 @@
   <mergeCells count="4">
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A15:B15"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -3104,7 +3104,7 @@
       <c r="I19" s="19" t="n"/>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="K19" s="11" t="n"/>

--- a/docs/요구사항_정의서_v1.0_CKD.xlsx
+++ b/docs/요구사항_정의서_v1.0_CKD.xlsx
@@ -2083,8 +2083,8 @@
   <mergeCells count="4">
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A1:B1"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="J30" s="11" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="K30" s="11" t="n"/>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="J32" s="11" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="K32" s="11" t="n"/>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="K33" s="11" t="n"/>

--- a/docs/요구사항_정의서_v1.0_CKD.xlsx
+++ b/docs/요구사항_정의서_v1.0_CKD.xlsx
@@ -2083,8 +2083,8 @@
   <mergeCells count="4">
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A15:B15"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="D3" s="19" t="inlineStr">
         <is>
-          <t>3초 이내</t>
+          <t>3초 이내 (실측 P95 18ms, 2026-06-01 부하 테스트)</t>
         </is>
       </c>
       <c r="E3" s="14" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>완료</t>
         </is>
       </c>
     </row>

--- a/docs/요구사항_정의서_v1.0_CKD.xlsx
+++ b/docs/요구사항_정의서_v1.0_CKD.xlsx
@@ -2083,8 +2083,8 @@
   <mergeCells count="4">
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A1:B1"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -2316,7 +2316,7 @@
       <c r="I4" s="19" t="n"/>
       <c r="J4" s="11" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="K4" s="11" t="n"/>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="J20" s="11" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="K20" s="11" t="n"/>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="J35" s="11" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="K35" s="11" t="n"/>
@@ -4017,7 +4017,7 @@
       <c r="I36" s="19" t="n"/>
       <c r="J36" s="11" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="K36" s="11" t="n"/>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="J38" s="11" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="K38" s="11" t="n"/>
@@ -4175,7 +4175,7 @@
       <c r="I39" s="19" t="n"/>
       <c r="J39" s="11" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="K39" s="11" t="n"/>
@@ -8218,7 +8218,7 @@
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>완료</t>
         </is>
       </c>
     </row>
@@ -8250,7 +8250,7 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>완료</t>
         </is>
       </c>
     </row>

--- a/docs/요구사항_정의서_v1.0_CKD.xlsx
+++ b/docs/요구사항_정의서_v1.0_CKD.xlsx
@@ -2083,8 +2083,8 @@
   <mergeCells count="4">
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A15:B15"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
-          <t>Rate limit 초과: HTTP 429</t>
+          <t>Rate limit 초과: HTTP 429 | 구현: slowapi 적용 (로그인·비밀번호재설정 5회/분, 일반 60회/분, 한국어 429)</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>완료</t>
         </is>
       </c>
     </row>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="D14" s="19" t="inlineStr">
         <is>
-          <t>1개 브레이크포인</t>
+          <t>1개 브레이크포인 | 구현: viewport meta + lg ≥1024px 점검, 1080px 고정폭 → max-w 변경</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>완료</t>
         </is>
       </c>
     </row>
@@ -7993,7 +7993,7 @@
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>완료</t>
         </is>
       </c>
     </row>
@@ -8025,7 +8025,7 @@
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>완료</t>
         </is>
       </c>
     </row>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>완료</t>
         </is>
       </c>
     </row>
@@ -8185,7 +8185,7 @@
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>완료</t>
         </is>
       </c>
     </row>
@@ -8282,7 +8282,7 @@
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>완료</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>완료</t>
         </is>
       </c>
     </row>

--- a/docs/요구사항_정의서_v1.0_CKD.xlsx
+++ b/docs/요구사항_정의서_v1.0_CKD.xlsx
@@ -2083,8 +2083,8 @@
   <mergeCells count="4">
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A1:B1"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="I38" s="19" t="inlineStr">
         <is>
-          <t>충전 모드(쉬어가기 모드)만 구현 — 트랙 강등(A→B)은 보류</t>
+          <t>충전 모드(쉬어가기 모드)만 구현 — 트랙 강등(A→B)은 보류 | v3.1 (2026-06-02): 5종 캐릭터 + 숙련도 배경</t>
         </is>
       </c>
       <c r="J38" s="11" t="inlineStr">
